--- a/sheets/Street-File.xlsx
+++ b/sheets/Street-File.xlsx
@@ -43,18 +43,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00C4A35A"/>
+      <color rgb="00FF9F1C"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="00111111"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="00111111"/>
       <sz val="10"/>
     </font>
     <font>
@@ -66,7 +66,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="009B1B2E"/>
+      <color rgb="00C41E3A"/>
       <sz val="12"/>
     </font>
     <font>
@@ -95,7 +95,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,12 +104,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A1A1A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7F1E6"/>
+        <fgColor rgb="00111111"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,12 +114,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009B1B2E"/>
+        <fgColor rgb="00C41E3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8EC"/>
+        <fgColor rgb="00FFF5E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,7 +129,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3338"/>
+        <fgColor rgb="001A1A1A"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,23 +143,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </bottom>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -172,10 +167,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -184,38 +179,38 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B9A989"/>
+        <color rgb="00DDDDDD"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="001A1A1A"/>
+        <color rgb="00111111"/>
       </left>
       <right style="medium">
-        <color rgb="001A1A1A"/>
+        <color rgb="00111111"/>
       </right>
       <top style="medium">
-        <color rgb="001A1A1A"/>
+        <color rgb="00111111"/>
       </top>
       <bottom style="medium">
-        <color rgb="001A1A1A"/>
+        <color rgb="00111111"/>
       </bottom>
     </border>
   </borders>
@@ -231,44 +226,44 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,81 +272,81 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -868,7 +863,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="009B1B2E"/>
+    <tabColor rgb="00C41E3A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1169,7 +1164,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>
@@ -1186,7 +1181,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001A1A1A"/>
+    <tabColor rgb="00111111"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1570,7 +1565,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>
@@ -1585,7 +1580,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001A1A1A"/>
+    <tabColor rgb="00111111"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2101,7 +2096,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001A1A1A"/>
+    <tabColor rgb="00111111"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2578,7 +2573,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>
@@ -2593,7 +2588,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="009B1B2E"/>
+    <tabColor rgb="00C41E3A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3266,7 +3261,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C4A35A"/>
+    <tabColor rgb="00FF9F1C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4153,7 +4148,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>
@@ -4682,7 +4677,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>
@@ -4697,7 +4692,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="009B1B2E"/>
+    <tabColor rgb="00C41E3A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4917,7 +4912,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>
@@ -5166,7 +5161,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002C3338"/>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5404,7 +5399,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LNC//NET STREET FILE  ·  unofficial table aid&amp;R&amp;A  ·  &amp;P/&amp;N</oddFooter>

--- a/sheets/Street-File.xlsx
+++ b/sheets/Street-File.xlsx
@@ -121,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -201,11 +201,80 @@
         <color rgb="00070A0E"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00070A0E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00070A0E"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00070A0E"/>
+      </right>
+      <top style="medium">
+        <color rgb="00070A0E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00070A0E"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00070A0E"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00070A0E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00070A0E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00070A0E"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00070A0E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -288,6 +357,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -377,61 +455,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="838200" cy="838200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="838200" cy="838200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -822,13 +845,6 @@
           <t xml:space="preserve">  STREET FILE   ·   META</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
@@ -854,15 +870,23 @@
           <t>Handle</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>DODGE</t>
+        </is>
+      </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Case No.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SF-76-VDR-MORA</t>
+        </is>
+      </c>
+      <c r="E3" s="38" t="n"/>
+      <c r="F3" s="39" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
@@ -876,15 +900,19 @@
           <t>Real Name</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Rafael Mora</t>
+        </is>
+      </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="7" t="n"/>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="39" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
@@ -898,15 +926,19 @@
           <t>Role / Rank</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Lawman 4</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Role 2 / Rank 2</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="E5" s="38" t="n"/>
+      <c r="F5" s="39" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -926,9 +958,13 @@
           <t>In-world date</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="39" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
@@ -954,11 +990,11 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Point buy 62/86 · HUM −2/non-fashion chrome · −4 Borgware (campaign)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="n"/>
+          <t>Point buy 62/86 · Neuroport not free (1000eb / HL 7) · company housing free · Backup = named, not dispatch · HUM −2/non-fashion chrome · −4 Borgware (campaign)</t>
+        </is>
+      </c>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="39" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -986,11 +1022,6 @@
           <t>RUNNING TOTALS  ·  source of truth (copy Cash / IP / Heat onto PDF page 2 after each session)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -1005,7 +1036,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="4" t="inlineStr">
@@ -1013,8 +1044,12 @@
           <t>Trauma Team / subs</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="7" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F10" s="39" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
@@ -1039,7 +1074,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="F11" s="39" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
@@ -1064,7 +1099,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="F12" s="39" t="n"/>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
@@ -1078,9 +1113,8 @@
           <t>IP earned (all-time)</t>
         </is>
       </c>
-      <c r="B13" s="5">
-        <f>SUM(LEDGER!G4:G43)</f>
-        <v/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="4" t="inlineStr">
@@ -1088,8 +1122,12 @@
           <t>ID / SIN</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Academy SIN — FLAGGED</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="n"/>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
@@ -1178,13 +1216,6 @@
           <t>Sync rule: PDF is truth for stats, skills, chrome, dossier. This book is truth for €$, IP, heat, people, jobs. After a session: add a LEDGER row, then copy B11 / B12 / B15 onto PDF page 2.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
@@ -1196,13 +1227,6 @@
           <t>Photos: Insert → Pictures into the boxes on the right (booking + known photograph). Acrobat does the same on PDF page 0.</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
@@ -1228,16 +1252,12 @@
           <t>BOOKING PHOTO</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="12" t="inlineStr">
         <is>
           <t>KNOWN PHOTOGRAPH</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
@@ -1250,16 +1270,16 @@
           <t>Insert booking photo</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
+      <c r="B22" s="40" t="n"/>
+      <c r="C22" s="41" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Insert street / known photo</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+      <c r="F22" s="40" t="n"/>
+      <c r="G22" s="41" t="n"/>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
@@ -1267,13 +1287,11 @@
       <c r="L22" s="3" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
+      <c r="A23" s="42" t="n"/>
+      <c r="C23" s="43" t="n"/>
       <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="G23" s="43" t="n"/>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
@@ -1281,13 +1299,11 @@
       <c r="L23" s="3" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
+      <c r="A24" s="42" t="n"/>
+      <c r="C24" s="43" t="n"/>
       <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="G24" s="43" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
@@ -1295,13 +1311,11 @@
       <c r="L24" s="3" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
+      <c r="A25" s="42" t="n"/>
+      <c r="C25" s="43" t="n"/>
       <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="G25" s="43" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
@@ -1309,13 +1323,11 @@
       <c r="L25" s="3" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="A26" s="42" t="n"/>
+      <c r="C26" s="43" t="n"/>
       <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="G26" s="43" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
@@ -1323,13 +1335,11 @@
       <c r="L26" s="3" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
+      <c r="A27" s="42" t="n"/>
+      <c r="C27" s="43" t="n"/>
       <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="G27" s="43" t="n"/>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
@@ -1337,13 +1347,11 @@
       <c r="L27" s="3" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+      <c r="A28" s="42" t="n"/>
+      <c r="C28" s="43" t="n"/>
       <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="G28" s="43" t="n"/>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
@@ -1351,13 +1359,11 @@
       <c r="L28" s="3" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+      <c r="A29" s="42" t="n"/>
+      <c r="C29" s="43" t="n"/>
       <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="G29" s="43" t="n"/>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
@@ -1365,13 +1371,13 @@
       <c r="L29" s="3" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
+      <c r="A30" s="44" t="n"/>
+      <c r="B30" s="45" t="n"/>
+      <c r="C30" s="46" t="n"/>
       <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+      <c r="E30" s="44" t="n"/>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="46" t="n"/>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
@@ -1493,7 +1499,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -1520,9 +1525,6 @@
           <t xml:space="preserve">  REF  ·  COMBAT  ·  CPR p.127–176, 186</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
@@ -1552,9 +1554,6 @@
           <t>Turn = 1 Move Action + 1 other Action. Round ≈ 3 seconds. Initiative = REF + 1d10. Move = MOVE × 2 m (or MOVE squares, diagonals OK).</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -1992,9 +1991,6 @@
           <t>WOUNDS  ·  ARMOR  ·  BRAWLING</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
@@ -2010,9 +2006,9 @@
           <t>Seriously Wounded: HP ≤ ⌈HP max / 2⌉. −2 to all Actions. Death Save = BODY. Mortally Wounded: HP 0. At start of your Turn roll 1d10 ≤ BODY or die. Each time you take damage while Mortal: Critical Injury +1 Death Save Penalty.</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
@@ -2028,9 +2024,9 @@
           <t>Armor: if damage &gt; SP, HP loss = damage − SP, then ablate SP by 1 (unless the attack says otherwise). Melee weapons ignore half SP (round up). Brawling does NOT. Ablate Head and Body separately.</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
@@ -2046,9 +2042,9 @@
           <t>Brawling DMG by BODY: ≤4 → 1d6 · 5–6 (or ≤4 with Cyberarm) → 2d6 · 7–10 → 3d6 · 11+ → 4d6. Cyberarm brawl is at least 2d6.</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
@@ -2064,9 +2060,9 @@
           <t>Facedown: both roll COOL + 1d10. Loser backs down or takes −2 on Checks against the winner until they beat them once. Cover: if they can see you, you are not in cover (bulletproof glass excepted).</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="B23" s="38" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
@@ -2082,9 +2078,9 @@
           <t>LUCK: spend 1:1 on a Check, resets each session. Extra Time: ×4 duration = +1 once. Complementary Skill: +1 once, no stack. Crit success: natural 10, add extra 1d10. Crit fail: natural 1, subtract extra 1d10.</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
@@ -2314,14 +2310,6 @@
           <t xml:space="preserve">  REF  ·  RANGE TABLES  ·  CPR p.173–174</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
       <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
@@ -2346,14 +2334,6 @@
           <t>Ranged: REF + weapon Skill + 1d10 vs DV by range (or vs DEX + Evasion + 1d10 if defender REF ≥ 8). Tie: defender wins. CPR p.173.</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
@@ -2364,14 +2344,6 @@
           <t>SINGLE SHOT DV</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
@@ -2734,14 +2706,6 @@
           <t>AUTOFIRE DV   ·   costs 10 bullets  ·   Autofire Skill  ·   damage 2d6 × amount you beat DV, cap = weapon Autofire (SMG 3 / AR 4)  ·  no Aimed Shot</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
-      <c r="I15" s="23" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
@@ -2860,14 +2824,6 @@
           <t>Shotgun shell: 1 attack vs DV13; every target you can see in 6 m cone takes 3d6 (roll once). No Aimed Shot.</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
@@ -2878,14 +2834,6 @@
           <t>Suppressive Fire: Action + 10 bullets. Everyone on foot, out of cover, in LOS, ≤25 m: WILL + Concentration + 1d10 vs your REF + Autofire + 1d10 or they must Move into cover.</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
@@ -2896,14 +2844,6 @@
           <t>Thrown weapons: ROF 1, REF + Athletics vs thrown range DV. Melee thrown does not halve SP. Grenades deal explosive damage in 10×10 m.</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
@@ -2914,14 +2854,6 @@
           <t>Arrows: loading is part of the attack (no Reload Action). Basic arrows can be retrieved.</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
@@ -3155,9 +3087,6 @@
           <t xml:space="preserve">  REF  ·  DIFFICULTY  ·  IP  ·  PRICES  ·  CPR p.129–130, 385, 411</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
@@ -3187,9 +3116,6 @@
           <t>STAT + Skill + 1d10 vs DV  (or vs defender STAT + Skill + 1d10). Tie: defender wins. No Skill: STAT + 1d10 only.</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -3459,9 +3385,6 @@
           <t>IMPROVEMENT POINTS  (spend between sessions)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -3611,9 +3534,6 @@
           <t>PRICE CATEGORIES  ·  without a Fixer you buy up to Premium only</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
@@ -3875,9 +3795,6 @@
           <t>Modifiers (subtract from your roll, they stack): night −1 · never done this −1 · complex −2 · no tools −2 · bad sleep −2 · extreme stress −2 · exhausted −4 · drunk/sedated −4 · secretly −4 · smoke/dark −4. Extra Time ×4 = +1. Complementary Skill = +1 once.</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
@@ -3961,8 +3878,8 @@
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -4008,16 +3925,6 @@
           <t xml:space="preserve">  INCIDENT LOG   ·   OPERATOR LEDGER</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
-      <c r="H1" s="9" t="n"/>
-      <c r="I1" s="9" t="n"/>
-      <c r="J1" s="9" t="n"/>
-      <c r="K1" s="9" t="n"/>
       <c r="L1" s="3" t="n"/>
     </row>
     <row r="2">
@@ -4093,17 +4000,55 @@
       <c r="L3" s="3" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Floor 22, Megabuilding H5</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>NCPD / Glen warrant</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>H5 Valentinos; IA; scav BD</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>burned</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>NCPD personal · Glen aide · H5 Valentinos</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Warrant: take alive. Three down in the hall. Badge pulled. Radio in the drawer.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Elena Ruiz (partner, on scene)</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -4672,7 +4617,6 @@
           <t>Session €$ (this sheet)</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
       <c r="C45" s="18">
         <f>SUM(F4:F43)</f>
         <v/>
@@ -4714,16 +4658,6 @@
           <t>In-world date, not real-world. Related persons should match CONTACTS handles. Heat = NCPD / corp / gang and a short note.</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="n"/>
     </row>
   </sheetData>
@@ -4783,15 +4717,6 @@
           <t xml:space="preserve">  KNOWN ASSOCIATES   ·   CREW FILE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
     </row>
@@ -4863,101 +4788,367 @@
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Elena Ruiz</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Elena Ruiz</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>NCPD beat</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Ex-partner. Did not cover Floor 22. Did not sell him.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Backup call; precinct door</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>She owes nothing. He owes the report.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Agent / HYW Vista locker</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Most poisonous phone on the list. Still picks up because Vista did not get better.</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Dwyer</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sgt. Frank Dwyer</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>NCPD desk, Heywood</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Old desk. Thinks the city is already dead.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Backup call; next-tier on a 6</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Dodge owes blood if heavies drop</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Heywood desk, not the radio net</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Named Backup Rank 4. A 6 on ETA is HIS people.</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Oz</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Marcus Osorio</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>NCPD beat, Vista</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Grew up on the same H5 stairs.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Backup call; street eyes on H5</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>even</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Vista beat / Mercado Sonora</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Rides while the bodies are “ours.”</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Kim Tran</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>NCPD beat</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>backup</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Other square. One call from duty.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Backup call (once)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>She owes one call. Second camera flash and she dumps the number.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Agent only</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Weakest link on the Rank 4 list. Do not burn her on a spectacle.</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>El Sereno</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(rumor — no booking)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Childhood stair-story, Megabuilding H5 after midnight.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Do not hunt. Do not sell.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>DO NOT TOUCH</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>H5 stairs after midnight</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Valued Person on the dossier. Myth Dodge made into a job. Not a choom.</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Los de H5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>(crew, not a name)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Valentinos, H5 / Mercado / La Catrina</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>The set that feeds the stack and moves bodies through La Catrina.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Heat; the notebook</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>war on the stack, not the whole family</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Sonora · La Catrina (Phalarope &amp; Plover)</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Floor 22 was theirs. Remaining names live in the jacket notebook.</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Glen aide</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(no booking yet)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>municipal / Glen</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Wanted the H5 mid-level alive. Got a process instead of a martyr.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Heat; why the badge came off</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>they wanted him living and discredited</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>The Glen / City Hall orbit</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Dirty politician lane. Do not make this a Valentinos war.</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
     </row>
@@ -5163,15 +5354,6 @@
           <t>Other PCs at the table + recurring NPCs. Dossier page 0 only keeps name-lists; this sheet is the actual cards. Trust 1 = will burn you, 5 = choomba.</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
     </row>
@@ -5380,11 +5562,6 @@
           <t xml:space="preserve">  NET   ·   INTERFACE / QUICKHACKS</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
@@ -5412,8 +5589,12 @@
           <t>Cyberdeck</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
-      <c r="C3" s="7" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C3" s="39" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Interface Rank</t>
@@ -5444,7 +5625,11 @@
           <t>Self-ICE / Passwalls</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
@@ -5461,7 +5646,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -5470,7 +5655,11 @@
           <t>Ex-Disks</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
@@ -5499,11 +5688,6 @@
           <t>PROGRAMS  /  HARDWARE</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -5737,11 +5921,6 @@
           <t>QUICKHACKS  ·  CEMK 2070s  ·  Interface + 1d10 vs DV   (CPR p.197 / CEMK RB p.16–18, 39)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
@@ -5798,8 +5977,8 @@
           <t>MOVE −1 for 60s; 0 MOVE = no Move Action</t>
         </is>
       </c>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="39" t="n"/>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
@@ -5826,8 +6005,8 @@
           <t>Damaged Ear crit (no bonus dmg) 60s</t>
         </is>
       </c>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="26" t="n"/>
+      <c r="E25" s="38" t="n"/>
+      <c r="F25" s="39" t="n"/>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
@@ -5854,8 +6033,8 @@
           <t>On fire: 4 HP at end of their Turn, bypass SP</t>
         </is>
       </c>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="39" t="n"/>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
@@ -5882,8 +6061,8 @@
           <t>GM picks 3 chrome pieces offline 60s</t>
         </is>
       </c>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="26" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="39" t="n"/>
       <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
@@ -5910,8 +6089,8 @@
           <t>You pick 1 chrome offline 60s (not Neuroport)</t>
         </is>
       </c>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="26" t="n"/>
+      <c r="E28" s="38" t="n"/>
+      <c r="F28" s="39" t="n"/>
       <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
@@ -5938,8 +6117,8 @@
           <t>Force their next Move; only if unaware</t>
         </is>
       </c>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="39" t="n"/>
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
@@ -5966,8 +6145,8 @@
           <t>MOVE −1d6 for 60s</t>
         </is>
       </c>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
+      <c r="E30" s="38" t="n"/>
+      <c r="F30" s="39" t="n"/>
       <c r="G30" s="3" t="n"/>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
@@ -5994,8 +6173,8 @@
           <t>3d6 HP, bypass armor, no ablation</t>
         </is>
       </c>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
+      <c r="E31" s="38" t="n"/>
+      <c r="F31" s="39" t="n"/>
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
@@ -6022,8 +6201,8 @@
           <t>You spend their next Action + Move</t>
         </is>
       </c>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
+      <c r="E32" s="38" t="n"/>
+      <c r="F32" s="39" t="n"/>
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
@@ -6050,8 +6229,8 @@
           <t>Eject 1 chipware into adjacent square</t>
         </is>
       </c>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="26" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="39" t="n"/>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
@@ -6078,8 +6257,8 @@
           <t>Unconscious 60s or until damaged; Prone</t>
         </is>
       </c>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="26" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="39" t="n"/>
       <c r="G34" s="3" t="n"/>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
@@ -6107,11 +6286,6 @@
           <t>Jack In: Interface + 1d10 vs target WILL + 1d10, 50 m, target must have a Neuroport. Failure still jacks in but they know. Eject: WILL + Concentration + 1d10 vs Interface + 1d10.</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
@@ -6180,15 +6354,6 @@
           <t xml:space="preserve">  GARAGE   ·   MOTO / FAMILY MOTORPOOL</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
     </row>
@@ -6219,8 +6384,8 @@
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="n"/>
+      <c r="E3" s="38" t="n"/>
+      <c r="F3" s="39" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
@@ -6234,15 +6399,6 @@
           <t>Moto Rank adds to Drive/Pilot and Vehicle Tech checks. Only one Family Vehicle out at a time (all of them at Rank 10). CPR p.161–164.</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
     </row>
@@ -6781,11 +6937,6 @@
           <t xml:space="preserve">  WORKSHOP   ·   MAKER</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
@@ -6927,11 +7078,6 @@
           <t>Each Maker Rank: +1 to two different specialties. Field Expertise also jury-rigs as an Action. CPR p.147–149.</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
@@ -6959,11 +7105,6 @@
           <t>JOBS  ·  repairs, upgrades, inventions</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
@@ -7197,11 +7338,6 @@
           <t>Upgrade/Fabricate/Invent DV by price: Cheap 9 / 1h · Costly 13 / 6h · Premium 17 / 1d · Expensive 21 / 1w · V.Exp 24 / 2w · Luxury 29 / 1mo · Super Luxury 29 / 1mo per 10,000eb.</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
@@ -7408,11 +7544,6 @@
           <t xml:space="preserve">  CLINIC   ·   MEDICINE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
@@ -7518,11 +7649,6 @@
           <t>Each Medicine Rank: +1 to one specialty. Surgery Skill = 2 per point (max 10). Installation, harvesting, bodysculpt, therapy: CPR p.149, 226.</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -7550,11 +7676,6 @@
           <t>PATIENTS  /  THERAPY  /  PHARMA</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -8014,17 +8135,6 @@
           <t xml:space="preserve">  TEAM   ·   EXEC TEAMWORK</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n"/>
@@ -8053,8 +8163,8 @@
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="n"/>
+      <c r="E3" s="38" t="n"/>
+      <c r="F3" s="39" t="n"/>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
@@ -8068,17 +8178,6 @@
           <t>Exec team members are mechanical NPCs, not just CONTACTS. Use cover job / true job. CPR p.153–157 for who you get at each Rank.</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -8623,11 +8722,6 @@
           <t xml:space="preserve">  WISHLIST   ·   NIGHT MARKET</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
@@ -8688,12 +8782,34 @@
       <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr"/>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="16" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Neuroport</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>cyberware</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Very Expensive</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Hospital / ripper</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>House rule: not free. HL 7 (2d6). Required for other chrome.</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
@@ -8702,12 +8818,34 @@
       <c r="L4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Self-ICE</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>cyberware</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Expensive</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Needs Neuroport. Quickhack Passwall.</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -8716,12 +8854,34 @@
       <c r="L5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>NCPD Crime Database</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>gear / Agent</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Expensive</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>stolen login / GM</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Skiptrace sugar. Badge is pulled — access is a plot.</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
@@ -8730,12 +8890,34 @@
       <c r="L6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Light Armorjack (Head)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>armor</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Night Market</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>If the mirrorshades stop being enough.</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -8744,12 +8926,34 @@
       <c r="L7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Basic Heavy Pistol ammo x50</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ammo</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Cheap</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>any</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Unity food.</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
@@ -8758,12 +8962,34 @@
       <c r="L8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="16" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Explosive Slug x10</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ammo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Fixer</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Satara barrel B.</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -8987,11 +9213,6 @@
           <t>Price categories (CPR p.385): Cheap 10 · Everyday 20 · Costly 50 · Premium 100 · Expensive 500 · Very Expensive 1,000 · Luxury 5,000 · Super Luxury 10,000+.</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>

--- a/sheets/Street-File.xlsx
+++ b/sheets/Street-File.xlsx
@@ -457,6 +457,61 @@
 </comments>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="838200" cy="838200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="838200" cy="838200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LEDGER" displayName="LEDGER" ref="A3:K43" headerRowCount="1">
   <autoFilter ref="A3:K43"/>
@@ -1499,6 +1554,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>

--- a/sheets/Street-File.xlsx
+++ b/sheets/Street-File.xlsx
@@ -509,6 +509,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2000250" cy="2800350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Booking" descr="Booking photo"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2000250" cy="2800350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Known" descr="Known photograph"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
